--- a/grupos/1CM - Estadisticos 20211.xlsx
+++ b/grupos/1CM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,16 +224,76 @@
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>PEREA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>FATIMA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AHUET</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>LOMAN</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
   </si>
   <si>
     <t>MATLATECATL</t>
@@ -242,262 +302,202 @@
     <t>MONTERO</t>
   </si>
   <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GRANADOS</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>MARES</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>PEREA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>PORTILLA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
-    <t>JESUS MANUEL</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>LETICIA ANETTE</t>
+  </si>
+  <si>
+    <t>ERANDI</t>
+  </si>
+  <si>
+    <t>PAZ AIDE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>ALONDRA VANNESSA</t>
   </si>
   <si>
     <t>LIZBETH</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
-    <t>EDUARDO</t>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
     <t>DULCE DANIELA</t>
   </si>
   <si>
     <t>MARIA DEL PILAR</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>FATIMA DEL ROSARIO</t>
+    <t>MICHELLE GUADALUPE</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>ALMA PATRICIA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
   </si>
   <si>
     <t>GETSEMANI GUADALUPE</t>
   </si>
   <si>
+    <t>NESTOR JOSUE</t>
+  </si>
+  <si>
+    <t>DIANA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JARITZA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>MIXTLI TONATI</t>
   </si>
   <si>
+    <t>MARIELA</t>
+  </si>
+  <si>
+    <t>HARUMI</t>
+  </si>
+  <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>MICHELLE GUADALUPE</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>ALMA PATRICIA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>NESTOR JOSUE</t>
-  </si>
-  <si>
-    <t>DIANA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JARITZA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>HARUMI</t>
   </si>
 </sst>
 </file>
@@ -1004,19 +1004,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1043,16 +1043,16 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1081,19 +1081,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1117,7 +1117,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1158,19 +1158,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1197,16 +1197,16 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1235,19 +1235,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1271,19 +1271,19 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1312,19 +1312,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1383,7 +1383,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1392,16 +1392,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1428,16 +1428,16 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1466,19 +1466,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1511,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1543,19 +1543,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1582,13 +1582,13 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1620,19 +1620,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1662,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1679,10 +1679,10 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1697,19 +1697,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1733,10 +1733,10 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1774,19 +1774,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1813,13 +1813,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1851,19 +1851,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1890,7 +1890,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1899,7 +1899,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1910,10 +1910,10 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -1922,7 +1922,7 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1931,13 +1931,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1964,19 +1964,19 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2005,19 +2005,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2050,10 +2050,10 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2067,16 +2067,16 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2121,16 +2121,16 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>-1</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2159,19 +2159,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2198,16 +2198,16 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2221,16 +2221,16 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2275,16 +2275,16 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2298,7 +2298,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -2313,16 +2313,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2349,10 +2349,10 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2375,13 +2375,13 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -2393,16 +2393,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2429,13 +2429,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2449,16 +2449,16 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>-1</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2467,19 +2467,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2503,16 +2503,16 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>-1</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2544,16 +2544,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2580,16 +2580,16 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2621,19 +2621,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2663,13 +2663,13 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2683,13 +2683,13 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>-1</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2737,13 +2737,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>-1</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2775,19 +2775,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2820,10 +2820,10 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2852,19 +2852,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2897,10 +2897,10 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2929,19 +2929,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2965,16 +2965,16 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3006,10 +3006,10 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3018,7 +3018,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3045,7 +3045,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3083,19 +3083,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3122,16 +3122,16 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3145,13 +3145,13 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>6</v>
@@ -3163,13 +3163,13 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3199,13 +3199,13 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3237,19 +3237,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3273,13 +3273,13 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3314,19 +3314,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3356,13 +3356,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3391,19 +3391,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3427,16 +3427,16 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3462,25 +3462,25 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3507,16 +3507,16 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3545,19 +3545,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3622,19 +3622,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3681,16 +3681,16 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>8</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G39">
         <v>6</v>
@@ -3699,19 +3699,19 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3735,16 +3735,16 @@
         <v>6</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>8</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3812,25 +3812,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>72.22</v>
+      </c>
+      <c r="G2">
+        <v>27.78</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>69.44</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>30.56</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3867,7 +3867,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3876,30 +3876,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>86.11</v>
+      </c>
+      <c r="G4">
+        <v>13.89</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>80.56</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.5</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>19.44</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3908,30 +3908,30 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>19.44</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3940,30 +3940,30 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>13.89</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -3975,22 +3975,22 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>91.67</v>
       </c>
       <c r="G7">
+        <v>8.33</v>
+      </c>
+      <c r="H7">
+        <v>7.7</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>8.6</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4000,7 +4000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4035,655 +4035,115 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920219</v>
+        <v>21330051920359</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920219</v>
+        <v>21330051920359</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920233</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920233</v>
+        <v>21330051920245</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920235</v>
+        <v>21330051920245</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920235</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920235</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920359</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920359</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920359</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920237</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920237</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920237</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920240</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920241</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920241</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920242</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920242</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920242</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920242</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920245</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920245</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920245</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>96</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920245</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920250</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920250</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920225</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920222</v>
-      </c>
-      <c r="B32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920222</v>
-      </c>
-      <c r="B33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920222</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4723,214 +4183,214 @@
         <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920242</v>
+        <v>21330051920245</v>
       </c>
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920245</v>
+        <v>21330051920219</v>
       </c>
       <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920219</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920235</v>
+        <v>21330051920215</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920237</v>
+        <v>21330051920216</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920222</v>
+        <v>21330051920217</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920233</v>
+        <v>21330051920218</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920241</v>
+        <v>21330051920220</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920250</v>
+        <v>21330051920221</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920240</v>
+        <v>21330051920230</v>
       </c>
       <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
         <v>72</v>
       </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920225</v>
+        <v>21330051920231</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920215</v>
+        <v>21330051920232</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>136</v>
@@ -4941,13 +4401,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920216</v>
+        <v>21330051920233</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>137</v>
@@ -4958,13 +4418,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920217</v>
+        <v>21330051920234</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>138</v>
@@ -4975,13 +4435,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920218</v>
+        <v>21330051920235</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -4992,13 +4452,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920220</v>
+        <v>21330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>140</v>
@@ -5009,13 +4469,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920221</v>
+        <v>21330051920237</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -5026,13 +4486,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920230</v>
+        <v>21330051920239</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>142</v>
@@ -5043,13 +4503,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920231</v>
+        <v>21330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
         <v>143</v>
@@ -5060,13 +4520,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920232</v>
+        <v>21330051920241</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
         <v>144</v>
@@ -5077,13 +4537,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920234</v>
+        <v>21330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -5094,13 +4554,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920236</v>
+        <v>21330051920244</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>146</v>
@@ -5111,13 +4571,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920239</v>
+        <v>21330051920246</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>147</v>
@@ -5128,13 +4588,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920243</v>
+        <v>21330051920247</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>148</v>
@@ -5145,13 +4605,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920244</v>
+        <v>21330051920248</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>149</v>
@@ -5162,13 +4622,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920246</v>
+        <v>21330051920249</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
         <v>150</v>
@@ -5179,13 +4639,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920247</v>
+        <v>21330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
         <v>151</v>
@@ -5196,13 +4656,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920248</v>
+        <v>21330051920229</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>152</v>
@@ -5213,13 +4673,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920249</v>
+        <v>21330051920228</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
@@ -5230,13 +4690,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920229</v>
+        <v>21330051920227</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>154</v>
@@ -5247,13 +4707,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920228</v>
+        <v>21330051920226</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>155</v>
@@ -5264,13 +4724,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920227</v>
+        <v>21330051920225</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>156</v>
@@ -5281,13 +4741,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920226</v>
+        <v>21330051920224</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -5298,13 +4758,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920224</v>
+        <v>21330051920223</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
@@ -5315,13 +4775,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920223</v>
+        <v>21330051920222</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
@@ -5337,7 +4797,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5369,39 +4829,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920233</v>
+        <v>21330051920250</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920233</v>
+        <v>21330051920250</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5410,21 +4870,21 @@
         <v>57</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920241</v>
+        <v>21330051920230</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5433,44 +4893,44 @@
         <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920241</v>
+        <v>21330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920240</v>
+        <v>21330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5479,7 +4939,7 @@
         <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5487,13 +4947,13 @@
         <v>21330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -5510,22 +4970,45 @@
         <v>21330051920225</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920222</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1CM - Estadisticos 20211.xlsx
+++ b/grupos/1CM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -191,10 +191,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>González Altamirano Victorino Juventino</t>
@@ -1001,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -1037,7 +1037,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1078,7 +1078,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -1155,7 +1155,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -1232,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1309,7 +1309,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>9</v>
@@ -1345,7 +1345,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>9</v>
@@ -1540,7 +1540,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1576,7 +1576,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1730,7 +1730,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1771,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1848,7 +1848,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1884,7 +1884,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1925,7 +1925,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -2038,7 +2038,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2079,7 +2079,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -2233,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2310,7 +2310,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2346,7 +2346,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2423,7 +2423,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2464,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>9</v>
@@ -2618,7 +2618,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2695,7 +2695,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2731,7 +2731,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2772,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2808,7 +2808,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2849,7 +2849,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2885,7 +2885,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2926,7 +2926,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2962,7 +2962,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3003,7 +3003,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>10</v>
@@ -3157,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3234,7 +3234,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3311,7 +3311,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3347,7 +3347,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3388,7 +3388,7 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3465,7 +3465,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -3542,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>9</v>
@@ -3619,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>7</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>7</v>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3812,19 +3812,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>72.22</v>
+        <v>69.44</v>
       </c>
       <c r="G2">
-        <v>27.78</v>
+        <v>30.56</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3844,19 +3844,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>80.56</v>
+        <v>72.22</v>
       </c>
       <c r="G3">
-        <v>19.44</v>
+        <v>27.78</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4797,7 +4797,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920250</v>
+        <v>21330051920240</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4852,22 +4852,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920250</v>
+        <v>21330051920240</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4875,19 +4875,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920230</v>
+        <v>21330051920241</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920240</v>
+        <v>21330051920241</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4921,19 +4921,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920241</v>
+        <v>21330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -4944,19 +4944,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920243</v>
+        <v>21330051920250</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920225</v>
+        <v>21330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4990,24 +4990,93 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920222</v>
+        <v>21330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920249</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920225</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920222</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20211.xlsx
+++ b/grupos/1CM - Estadisticos 20211.xlsx
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -3015,7 +3015,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -3051,7 +3051,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3246,7 +3246,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -3984,7 +3984,7 @@
         <v>8.33</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1CM - Estadisticos 20211.xlsx
+++ b/grupos/1CM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -191,24 +191,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
+    <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,22 +221,139 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AHUET</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOMAN</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
     <t>PALMA</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GRANADOS</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
   </si>
   <si>
     <t>RANGEL</t>
@@ -245,220 +362,103 @@
     <t>PEREA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>LETICIA ANETTE</t>
+  </si>
+  <si>
+    <t>ERANDI</t>
+  </si>
+  <si>
+    <t>PAZ AIDE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
     <t>JESUS MANUEL</t>
   </si>
   <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>ALONDRA VANNESSA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
   </si>
   <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>MARIA DEL PILAR</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
   </si>
   <si>
+    <t>MICHELLE GUADALUPE</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>FATIMA DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>MICHELLE GUADALUPE</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -1019,22 +1019,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1043,10 +1043,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1096,34 +1096,34 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1173,22 +1173,22 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1206,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1250,40 +1250,40 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1327,22 +1327,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1351,13 +1351,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1389,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1404,37 +1404,37 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1481,22 +1481,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1558,40 +1558,40 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1635,37 +1635,37 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1712,25 +1712,25 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1780,7 +1780,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1789,37 +1789,37 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1857,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1866,40 +1866,40 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1940,28 +1940,28 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -1970,10 +1970,10 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2020,22 +2020,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2053,7 +2053,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2064,13 +2064,13 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2082,52 +2082,52 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2174,40 +2174,40 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2236,43 +2236,43 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2325,43 +2325,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>7</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2390,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2405,25 +2405,25 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2432,7 +2432,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2455,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>6</v>
@@ -2473,7 +2473,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2482,40 +2482,40 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2556,40 +2556,40 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2636,22 +2636,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2660,16 +2660,16 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2680,13 +2680,13 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -2698,55 +2698,55 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2790,22 +2790,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2867,34 +2867,34 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2944,40 +2944,40 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3012,7 +3012,7 @@
         <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -3021,37 +3021,37 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3098,22 +3098,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3128,7 +3128,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3160,55 +3160,55 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3252,22 +3252,22 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3329,22 +3329,22 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3406,22 +3406,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3477,37 +3477,37 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>6</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3560,22 +3560,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3593,7 +3593,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3637,40 +3637,40 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>7</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>9</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3708,43 +3708,43 @@
         <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3812,19 +3812,19 @@
         <v>36</v>
       </c>
       <c r="D2">
+        <v>27</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>75</v>
+      </c>
+      <c r="G2">
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>69.44</v>
-      </c>
-      <c r="G2">
-        <v>30.56</v>
-      </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3844,19 +3844,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>72.22</v>
+        <v>80.56</v>
       </c>
       <c r="G3">
-        <v>27.78</v>
+        <v>19.44</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3888,7 +3888,7 @@
         <v>13.89</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3908,30 +3908,30 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="G5">
-        <v>2.78</v>
+        <v>5.56</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3940,30 +3940,30 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -3972,19 +3972,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4000,7 +4000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,126 +4025,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920359</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920359</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920242</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920245</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920245</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4180,81 +4060,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920359</v>
+        <v>21330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920245</v>
+        <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920219</v>
+        <v>21330051920217</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920242</v>
+        <v>21330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920215</v>
+        <v>21330051920219</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>128</v>
@@ -4265,13 +4145,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920216</v>
+        <v>21330051920220</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>129</v>
@@ -4282,13 +4162,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920217</v>
+        <v>21330051920221</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>130</v>
@@ -4299,13 +4179,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920218</v>
+        <v>21330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
@@ -4316,13 +4196,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920220</v>
+        <v>21330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>132</v>
@@ -4333,13 +4213,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920221</v>
+        <v>21330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>133</v>
@@ -4350,13 +4230,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920230</v>
+        <v>21330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>134</v>
@@ -4367,13 +4247,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920231</v>
+        <v>21330051920234</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>135</v>
@@ -4384,13 +4264,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>136</v>
@@ -4401,13 +4281,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920233</v>
+        <v>21330051920236</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
         <v>137</v>
@@ -4418,13 +4298,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920234</v>
+        <v>21330051920359</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>138</v>
@@ -4435,13 +4315,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920235</v>
+        <v>21330051920237</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>139</v>
@@ -4452,13 +4332,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920236</v>
+        <v>21330051920239</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>140</v>
@@ -4469,13 +4349,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920237</v>
+        <v>21330051920240</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -4486,13 +4366,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920239</v>
+        <v>21330051920241</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
         <v>142</v>
@@ -4503,13 +4383,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920240</v>
+        <v>21330051920242</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>143</v>
@@ -4520,13 +4400,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920241</v>
+        <v>21330051920243</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>144</v>
@@ -4537,13 +4417,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920243</v>
+        <v>21330051920244</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>145</v>
@@ -4554,10 +4434,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920244</v>
+        <v>21330051920245</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>113</v>
@@ -4574,10 +4454,10 @@
         <v>21330051920246</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>147</v>
@@ -4591,10 +4471,10 @@
         <v>21330051920247</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>148</v>
@@ -4608,10 +4488,10 @@
         <v>21330051920248</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>149</v>
@@ -4625,10 +4505,10 @@
         <v>21330051920249</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>150</v>
@@ -4642,10 +4522,10 @@
         <v>21330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
         <v>151</v>
@@ -4659,10 +4539,10 @@
         <v>21330051920229</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
         <v>152</v>
@@ -4676,10 +4556,10 @@
         <v>21330051920228</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
@@ -4693,10 +4573,10 @@
         <v>21330051920227</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>154</v>
@@ -4710,10 +4590,10 @@
         <v>21330051920226</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>155</v>
@@ -4727,10 +4607,10 @@
         <v>21330051920225</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
         <v>156</v>
@@ -4744,10 +4624,10 @@
         <v>21330051920224</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -4761,10 +4641,10 @@
         <v>21330051920223</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
@@ -4778,10 +4658,10 @@
         <v>21330051920222</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
@@ -4797,7 +4677,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4829,22 +4709,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4852,22 +4732,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4875,22 +4755,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920241</v>
+        <v>21330051920242</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4898,22 +4778,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920241</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4921,19 +4801,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920250</v>
+        <v>21330051920240</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -4944,16 +4824,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920250</v>
+        <v>21330051920241</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4967,22 +4847,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920230</v>
+        <v>21330051920249</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4990,93 +4870,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920243</v>
+        <v>21330051920225</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920249</v>
-      </c>
-      <c r="B10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920225</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920222</v>
-      </c>
-      <c r="B12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
